--- a/Data/RemapDrafts/KleeRemapDraft.xlsx
+++ b/Data/RemapDrafts/KleeRemapDraft.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Computer\Games\Genshin\Repos\Repos\Fix-Raiden-Boss\Data\RemapDrafts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84526C6-74B4-48B8-BF96-AE7DEEB13F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D187762-2FBC-4475-9A35-65B0CEA73878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{486FC702-9158-49C7-B749-9EA64B7B4824}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" activeTab="1" xr2:uid="{486FC702-9158-49C7-B749-9EA64B7B4824}"/>
   </bookViews>
   <sheets>
-    <sheet name="V4.0 Klee to BlossomStarlight" sheetId="1" r:id="rId1"/>
-    <sheet name="V4.0 BlossomStarlight to Klee" sheetId="2" r:id="rId2"/>
+    <sheet name="Credits" sheetId="3" r:id="rId1"/>
+    <sheet name="V4.0 Klee to BlossomStarlight" sheetId="1" r:id="rId2"/>
+    <sheet name="V4.0 BlossomStarlight to Klee" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V4.0 BlossomStarlight to Klee'!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'V4.0 Klee to BlossomStarlight'!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'V4.0 BlossomStarlight to Klee'!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V4.0 Klee to BlossomStarlight'!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
   <si>
     <t>Uncertainty</t>
   </si>
@@ -233,13 +234,22 @@
   </si>
   <si>
     <t>KleeBlossomStarlight's left toes</t>
+  </si>
+  <si>
+    <t>Authors</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>AlbertGold#2696</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -250,6 +260,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -273,17 +299,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
@@ -636,16 +666,47 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B377D998-AD1E-4C57-80FF-83345567294E}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="26" x14ac:dyDescent="0.6">
+      <c r="A1" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" xr:uid="{B5B4BEC1-13EF-43F8-96DF-D6D741C973DB}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6053A246-5513-40B8-A6A8-6B9BC5A9DEF3}">
   <dimension ref="A1:D95"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.140625" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" customWidth="1"/>
-    <col min="4" max="4" width="74.140625" customWidth="1"/>
+    <col min="2" max="2" width="26.1796875" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="4" max="4" width="74.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -659,7 +720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -668,7 +729,7 @@
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -677,7 +738,7 @@
       </c>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -686,7 +747,7 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -695,7 +756,7 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -704,7 +765,7 @@
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -713,7 +774,7 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -722,7 +783,7 @@
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -736,7 +797,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -750,7 +811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -759,7 +820,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -770,7 +831,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -779,7 +840,7 @@
       </c>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -788,7 +849,7 @@
       </c>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -797,7 +858,7 @@
       </c>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -806,7 +867,7 @@
       </c>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
@@ -815,7 +876,7 @@
       </c>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
@@ -824,7 +885,7 @@
       </c>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
@@ -833,7 +894,7 @@
       </c>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
@@ -842,7 +903,7 @@
       </c>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
@@ -851,7 +912,7 @@
       </c>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
@@ -860,7 +921,7 @@
       </c>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
@@ -869,7 +930,7 @@
       </c>
       <c r="D23" s="2"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
@@ -880,7 +941,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
@@ -891,7 +952,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
@@ -900,7 +961,7 @@
       </c>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
@@ -909,7 +970,7 @@
       </c>
       <c r="D27" s="2"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
@@ -918,7 +979,7 @@
       </c>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>27</v>
       </c>
@@ -927,7 +988,7 @@
       </c>
       <c r="D29" s="2"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>28</v>
       </c>
@@ -936,7 +997,7 @@
       </c>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>29</v>
       </c>
@@ -945,7 +1006,7 @@
       </c>
       <c r="D31" s="2"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>30</v>
       </c>
@@ -954,7 +1015,7 @@
       </c>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>31</v>
       </c>
@@ -963,7 +1024,7 @@
       </c>
       <c r="D33" s="2"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>32</v>
       </c>
@@ -972,7 +1033,7 @@
       </c>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>33</v>
       </c>
@@ -981,7 +1042,7 @@
       </c>
       <c r="D35" s="2"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>34</v>
       </c>
@@ -990,7 +1051,7 @@
       </c>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>35</v>
       </c>
@@ -999,7 +1060,7 @@
       </c>
       <c r="D37" s="2"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1008,7 +1069,7 @@
       </c>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>37</v>
       </c>
@@ -1017,7 +1078,7 @@
       </c>
       <c r="D39" s="2"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1026,7 +1087,7 @@
       </c>
       <c r="D40" s="2"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>39</v>
       </c>
@@ -1035,7 +1096,7 @@
       </c>
       <c r="D41" s="2"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>40</v>
       </c>
@@ -1046,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>41</v>
       </c>
@@ -1057,7 +1118,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>42</v>
       </c>
@@ -1068,7 +1129,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>43</v>
       </c>
@@ -1079,7 +1140,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>44</v>
       </c>
@@ -1088,7 +1149,7 @@
       </c>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>45</v>
       </c>
@@ -1097,7 +1158,7 @@
       </c>
       <c r="D47" s="2"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>46</v>
       </c>
@@ -1106,7 +1167,7 @@
       </c>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>47</v>
       </c>
@@ -1115,7 +1176,7 @@
       </c>
       <c r="D49" s="2"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>48</v>
       </c>
@@ -1124,7 +1185,7 @@
       </c>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>49</v>
       </c>
@@ -1133,7 +1194,7 @@
       </c>
       <c r="D51" s="2"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>50</v>
       </c>
@@ -1142,7 +1203,7 @@
       </c>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>51</v>
       </c>
@@ -1151,7 +1212,7 @@
       </c>
       <c r="D53" s="2"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>52</v>
       </c>
@@ -1160,7 +1221,7 @@
       </c>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>53</v>
       </c>
@@ -1169,7 +1230,7 @@
       </c>
       <c r="D55" s="2"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>54</v>
       </c>
@@ -1178,7 +1239,7 @@
       </c>
       <c r="D56" s="2"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>55</v>
       </c>
@@ -1187,7 +1248,7 @@
       </c>
       <c r="D57" s="2"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>56</v>
       </c>
@@ -1196,7 +1257,7 @@
       </c>
       <c r="D58" s="2"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>57</v>
       </c>
@@ -1205,7 +1266,7 @@
       </c>
       <c r="D59" s="2"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>58</v>
       </c>
@@ -1214,7 +1275,7 @@
       </c>
       <c r="D60" s="2"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>59</v>
       </c>
@@ -1223,7 +1284,7 @@
       </c>
       <c r="D61" s="2"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>60</v>
       </c>
@@ -1234,7 +1295,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>61</v>
       </c>
@@ -1245,7 +1306,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>62</v>
       </c>
@@ -1259,7 +1320,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>63</v>
       </c>
@@ -1270,7 +1331,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>64</v>
       </c>
@@ -1284,7 +1345,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>65</v>
       </c>
@@ -1298,7 +1359,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>66</v>
       </c>
@@ -1312,7 +1373,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>67</v>
       </c>
@@ -1323,7 +1384,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>68</v>
       </c>
@@ -1332,7 +1393,7 @@
       </c>
       <c r="D70" s="2"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>69</v>
       </c>
@@ -1343,7 +1404,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>70</v>
       </c>
@@ -1352,7 +1413,7 @@
       </c>
       <c r="D72" s="2"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>71</v>
       </c>
@@ -1363,7 +1424,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>72</v>
       </c>
@@ -1372,7 +1433,7 @@
       </c>
       <c r="D74" s="2"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>73</v>
       </c>
@@ -1383,7 +1444,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>74</v>
       </c>
@@ -1392,7 +1453,7 @@
       </c>
       <c r="D76" s="2"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>75</v>
       </c>
@@ -1403,7 +1464,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>76</v>
       </c>
@@ -1412,7 +1473,7 @@
       </c>
       <c r="D78" s="2"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>77</v>
       </c>
@@ -1423,7 +1484,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>78</v>
       </c>
@@ -1432,7 +1493,7 @@
       </c>
       <c r="D80" s="2"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>79</v>
       </c>
@@ -1443,7 +1504,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>80</v>
       </c>
@@ -1452,7 +1513,7 @@
       </c>
       <c r="D82" s="2"/>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>81</v>
       </c>
@@ -1463,7 +1524,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>82</v>
       </c>
@@ -1472,7 +1533,7 @@
       </c>
       <c r="D84" s="2"/>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>83</v>
       </c>
@@ -1483,7 +1544,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>84</v>
       </c>
@@ -1492,7 +1553,7 @@
       </c>
       <c r="D86" s="2"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>85</v>
       </c>
@@ -1503,7 +1564,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>86</v>
       </c>
@@ -1514,7 +1575,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>87</v>
       </c>
@@ -1525,7 +1586,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>88</v>
       </c>
@@ -1536,7 +1597,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>89</v>
       </c>
@@ -1547,7 +1608,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>90</v>
       </c>
@@ -1558,7 +1619,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>91</v>
       </c>
@@ -1569,7 +1630,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>92</v>
       </c>
@@ -1580,7 +1641,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>93</v>
       </c>
@@ -1599,18 +1660,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73CA0B00-4D3A-4A85-A7E3-61D458FB017B}">
   <dimension ref="A1:D93"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" customWidth="1"/>
+    <col min="1" max="1" width="25.81640625" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="53.28515625" customWidth="1"/>
+    <col min="3" max="3" width="19.26953125" customWidth="1"/>
+    <col min="4" max="4" width="53.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1624,7 +1685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1632,7 +1693,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1646,7 +1707,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1657,7 +1718,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1668,7 +1729,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1679,7 +1740,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1687,7 +1748,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1695,7 +1756,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1703,7 +1764,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1711,7 +1772,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1719,7 +1780,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1727,7 +1788,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1735,7 +1796,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1743,7 +1804,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1751,7 +1812,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1759,7 +1820,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1767,7 +1828,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1775,7 +1836,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1783,7 +1844,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1791,7 +1852,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1802,7 +1863,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1813,7 +1874,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1824,7 +1885,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1835,7 +1896,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1846,7 +1907,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1854,7 +1915,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1865,7 +1926,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1873,7 +1934,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1884,7 +1945,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1892,7 +1953,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1903,7 +1964,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>30</v>
       </c>
@@ -1911,7 +1972,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>31</v>
       </c>
@@ -1922,7 +1983,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>32</v>
       </c>
@@ -1930,7 +1991,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>33</v>
       </c>
@@ -1941,7 +2002,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>34</v>
       </c>
@@ -1949,7 +2010,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1960,7 +2021,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1968,7 +2029,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>37</v>
       </c>
@@ -1979,7 +2040,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1987,7 +2048,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>39</v>
       </c>
@@ -1998,7 +2059,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>40</v>
       </c>
@@ -2009,7 +2070,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>41</v>
       </c>
@@ -2020,7 +2081,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>42</v>
       </c>
@@ -2031,7 +2092,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>43</v>
       </c>
@@ -2039,7 +2100,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>44</v>
       </c>
@@ -2047,7 +2108,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>45</v>
       </c>
@@ -2055,7 +2116,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>46</v>
       </c>
@@ -2063,7 +2124,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>47</v>
       </c>
@@ -2071,7 +2132,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>48</v>
       </c>
@@ -2079,7 +2140,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>49</v>
       </c>
@@ -2087,7 +2148,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>50</v>
       </c>
@@ -2095,7 +2156,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>51</v>
       </c>
@@ -2103,7 +2164,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>52</v>
       </c>
@@ -2111,7 +2172,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>53</v>
       </c>
@@ -2119,7 +2180,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>54</v>
       </c>
@@ -2127,7 +2188,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>55</v>
       </c>
@@ -2135,7 +2196,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>56</v>
       </c>
@@ -2143,7 +2204,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>57</v>
       </c>
@@ -2151,7 +2212,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>58</v>
       </c>
@@ -2159,7 +2220,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>59</v>
       </c>
@@ -2167,7 +2228,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>60</v>
       </c>
@@ -2175,7 +2236,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>61</v>
       </c>
@@ -2186,7 +2247,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>62</v>
       </c>
@@ -2197,7 +2258,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>63</v>
       </c>
@@ -2205,7 +2266,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>64</v>
       </c>
@@ -2213,7 +2274,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>65</v>
       </c>
@@ -2224,7 +2285,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>66</v>
       </c>
@@ -2232,7 +2293,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>67</v>
       </c>
@@ -2243,7 +2304,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>68</v>
       </c>
@@ -2254,7 +2315,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>69</v>
       </c>
@@ -2262,7 +2323,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>70</v>
       </c>
@@ -2270,7 +2331,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>71</v>
       </c>
@@ -2278,7 +2339,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>72</v>
       </c>
@@ -2286,7 +2347,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>73</v>
       </c>
@@ -2294,7 +2355,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>74</v>
       </c>
@@ -2302,7 +2363,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>75</v>
       </c>
@@ -2310,7 +2371,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>76</v>
       </c>
@@ -2318,7 +2379,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>77</v>
       </c>
@@ -2326,7 +2387,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>78</v>
       </c>
@@ -2334,7 +2395,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>79</v>
       </c>
@@ -2342,7 +2403,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>80</v>
       </c>
@@ -2350,7 +2411,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>81</v>
       </c>
@@ -2358,7 +2419,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>82</v>
       </c>
@@ -2366,7 +2427,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>83</v>
       </c>
@@ -2374,7 +2435,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>84</v>
       </c>
@@ -2382,7 +2443,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>85</v>
       </c>
@@ -2393,7 +2454,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>86</v>
       </c>
@@ -2401,7 +2462,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>87</v>
       </c>
@@ -2412,7 +2473,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>88</v>
       </c>
@@ -2423,7 +2484,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>89</v>
       </c>
@@ -2431,7 +2492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>90</v>
       </c>
@@ -2439,7 +2500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>91</v>
       </c>
